--- a/etf_holdings/2026-10-27_common_holdings_all.xlsx
+++ b/etf_holdings/2026-10-27_common_holdings_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP5"/>
+  <dimension ref="A1:AP2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,11 +649,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.34%</t>
+          <t>11.75%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>12671000</v>
+        <v>13046000</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>14.69%</t>
+          <t>14.77%</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -701,7 +701,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>14.50%</t>
+          <t>14.63%</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -753,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="AD2" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>9.72%</t>
+          <t>9.75%</t>
         </is>
       </c>
       <c r="AG2" t="n">
@@ -792,7 +792,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>9.01%</t>
+          <t>9.05%</t>
         </is>
       </c>
       <c r="AM2" t="n">
@@ -800,573 +800,15 @@
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>110.13%</t>
+          <t>110.86%</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>9.18%</t>
+          <t>9.24%</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
-        <is>
-          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A,00405A,00407A,00993A,00400A</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2383</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>12</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>8.23%</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>4328000</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>10.04%</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>3.81%</t>
-        </is>
-      </c>
-      <c r="L3" t="n">
-        <v>144000</v>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>3.25%</t>
-        </is>
-      </c>
-      <c r="O3" t="n">
-        <v>309000</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>4.80%</t>
-        </is>
-      </c>
-      <c r="R3" t="n">
-        <v>1200000</v>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>2.80%</t>
-        </is>
-      </c>
-      <c r="U3" t="n">
-        <v>165000</v>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>4.52%</t>
-        </is>
-      </c>
-      <c r="X3" t="n">
-        <v>420000</v>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>1.95%</t>
-        </is>
-      </c>
-      <c r="AA3" t="n">
-        <v>134000</v>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>4.97%</t>
-        </is>
-      </c>
-      <c r="AD3" t="n">
-        <v>212000</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>5.60%</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>225000</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>4.82%</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>93000</v>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>台光電</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>4.30%</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>254000</v>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>59.09%</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>4.92%</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A,00405A,00407A,00993A,00400A</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2454</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>12</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>7.74%</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>5143000</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>6.18%</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>1050000</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>5.47%</t>
-        </is>
-      </c>
-      <c r="L4" t="n">
-        <v>249000</v>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>6.85%</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>786000</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>4.75%</t>
-        </is>
-      </c>
-      <c r="R4" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>1.43%</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>102000</v>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>1.60%</t>
-        </is>
-      </c>
-      <c r="X4" t="n">
-        <v>179000</v>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>1.99%</t>
-        </is>
-      </c>
-      <c r="AA4" t="n">
-        <v>165000</v>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>5.46%</t>
-        </is>
-      </c>
-      <c r="AD4" t="n">
-        <v>294000</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>5.30%</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>269000</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2.97%</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>69000</v>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>聯發科</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>6.89%</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
-        <v>514000</v>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>56.63%</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>4.72%</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A,00405A,00407A,00993A,00400A</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>3017</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>12</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>7.62%</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>6457000</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>6.23%</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>1350000</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2.30%</t>
-        </is>
-      </c>
-      <c r="L5" t="n">
-        <v>134000</v>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2.55%</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>374000</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>5.65%</t>
-        </is>
-      </c>
-      <c r="R5" t="n">
-        <v>2275000</v>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>1.59%</t>
-        </is>
-      </c>
-      <c r="U5" t="n">
-        <v>145000</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>6.43%</t>
-        </is>
-      </c>
-      <c r="X5" t="n">
-        <v>921000</v>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>1.49%</t>
-        </is>
-      </c>
-      <c r="AA5" t="n">
-        <v>158000</v>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>4.05%</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>278000</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>5.79%</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>375000</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>4.03%</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>120000</v>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>奇鋐</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>3.46%</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>329000</v>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>51.19%</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>4.27%</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
         <is>
           <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A,00405A,00407A,00993A,00400A</t>
         </is>

--- a/etf_holdings/2026-10-27_common_holdings_all.xlsx
+++ b/etf_holdings/2026-10-27_common_holdings_all.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP2"/>
+  <dimension ref="A1:AP5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -809,6 +809,564 @@
         </is>
       </c>
       <c r="AP2" t="inlineStr">
+        <is>
+          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A,00405A,00407A,00993A,00400A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>12</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>7.72%</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>4328000</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>9.40%</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>3.81%</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>144000</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3.25%</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>309000</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>4.51%</t>
+        </is>
+      </c>
+      <c r="R3" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2.80%</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>165000</v>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>4.52%</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>420000</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>1.95%</t>
+        </is>
+      </c>
+      <c r="AA3" t="n">
+        <v>134000</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>4.74%</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>212000</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>5.23%</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>225000</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>4.82%</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>93000</v>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>4.02%</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>254000</v>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>56.77%</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>4.73%</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A,00405A,00407A,00993A,00400A</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>12</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>7.78%</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>5233000</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>6.09%</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5.47%</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>249000</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>6.85%</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>786000</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>4.70%</t>
+        </is>
+      </c>
+      <c r="R4" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>1.43%</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>102000</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>1.60%</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>179000</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>1.99%</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>165000</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>5.48%</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>294000</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>5.21%</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>269000</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2.97%</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>69000</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>6.79%</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>514000</v>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>56.36%</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>4.70%</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A,00405A,00407A,00993A,00400A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>7.68%</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>6537000</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6.19%</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>1350000</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2.30%</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>134000</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2.55%</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>374000</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>5.77%</t>
+        </is>
+      </c>
+      <c r="R5" t="n">
+        <v>2330000</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>1.59%</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>145000</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>6.43%</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>921000</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>1.49%</t>
+        </is>
+      </c>
+      <c r="AA5" t="n">
+        <v>158000</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1.89%</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>128000</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>5.75%</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>375000</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>4.03%</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>120000</v>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>3.43%</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>329000</v>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>49.10%</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>4.09%</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>00981A,00991A,00980A,00982A,00403A,00985A,00992A,00990A,00405A,00407A,00993A,00400A</t>
         </is>
